--- a/outputs/daily/hr_rankings_2026-07-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-11.xlsx
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2226,34 +2222,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8587,56 +8579,56 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>804668</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Rafael Flores Jr.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>58.3</v>
+        <v>58.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8650,26 +8642,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>51.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>51.2</v>
+        <v>32.8</v>
       </c>
       <c r="R30" t="n">
-        <v>68.09999999999999</v>
+        <v>47.8</v>
       </c>
       <c r="S30" t="n">
-        <v>76.2</v>
+        <v>64.3</v>
       </c>
       <c r="T30" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U30" t="n">
-        <v>73.2</v>
+        <v>63.3</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8683,7 +8675,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8704,7 +8696,7 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr"/>
@@ -8716,32 +8708,32 @@
       </c>
       <c r="AG30" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/7 over last 3 games</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8751,112 +8743,112 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>15.44</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>45.73</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>90.37</t>
+          <t>91.58</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>102.6264</t>
+          <t>102.6343</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4734</t>
+          <t>0.7821</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>0.3984</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3377</t>
+          <t>0.522</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>71.44</t>
+          <t>53.88</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1825</t>
+          <t>0.4396</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3711</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8867,52 +8859,52 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>804668</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rafael Flores Jr.</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -8930,26 +8922,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>72.59999999999999</v>
+        <v>51.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>32.8</v>
+        <v>51.2</v>
       </c>
       <c r="R31" t="n">
-        <v>47.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>64.3</v>
+        <v>76.2</v>
       </c>
       <c r="T31" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>63.3</v>
+        <v>70.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8963,7 +8955,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -8984,7 +8976,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -8996,32 +8988,32 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Contact streak: 3/7 over last 3 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9031,112 +9023,112 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>15.44</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>45.73</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>91.58</t>
+          <t>90.37</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>102.6343</t>
+          <t>102.6264</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.7821</t>
+          <t>0.4734</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.3984</t>
+          <t>0.212</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>0.3377</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>53.88</t>
+          <t>71.44</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>26.86</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.4396</t>
+          <t>0.1825</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.99</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.3711</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -11482,34 +11474,30 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12050,34 +12038,30 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16248,28 +16232,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y57" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19515,22 +19503,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -19545,22 +19533,22 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Joe Ryan</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>657746</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -19578,26 +19566,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>33.6</v>
+        <v>57</v>
       </c>
       <c r="Q69" t="n">
-        <v>51.2</v>
+        <v>31.6</v>
       </c>
       <c r="R69" t="n">
-        <v>68.09999999999999</v>
+        <v>40.1</v>
       </c>
       <c r="S69" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T69" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U69" t="n">
-        <v>52.3</v>
+        <v>7</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19611,7 +19599,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19632,7 +19620,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -19649,27 +19637,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
@@ -19679,112 +19667,112 @@
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>47.82</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>100.1077</t>
+          <t>102.7141</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.5116</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.2285</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>30.11</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.2416</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>42.74</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.3711</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19795,47 +19783,47 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>694212</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Samuel Basallo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19858,61 +19846,65 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>57</v>
+        <v>49.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>31.6</v>
+        <v>42.9</v>
       </c>
       <c r="R70" t="n">
-        <v>40.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S70" t="n">
-        <v>93.2</v>
+        <v>59.8</v>
       </c>
       <c r="T70" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -19929,27 +19921,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
@@ -19959,112 +19951,112 @@
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>47.82</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.64</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>102.7141</t>
+          <t>102.5598</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.5116</t>
+          <t>0.4464</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.2285</t>
+          <t>0.2043</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3232</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.94</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>49.93</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>42.25</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>29.47</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>0.2416</t>
+          <t>0.1972</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20075,56 +20067,56 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>694212</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Samuel Basallo</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Joe Ryan</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>657746</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -20138,65 +20130,61 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>49.6</v>
+        <v>33.6</v>
       </c>
       <c r="Q71" t="n">
-        <v>42.9</v>
+        <v>51.2</v>
       </c>
       <c r="R71" t="n">
         <v>68.09999999999999</v>
       </c>
       <c r="S71" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T71" t="n">
         <v>50</v>
       </c>
       <c r="U71" t="n">
-        <v>62</v>
+        <v>50.3</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr"/>
@@ -20213,27 +20201,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.1% barrel, 14.8 HR allowed</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
@@ -20243,97 +20231,97 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>90.64</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>102.5598</t>
+          <t>100.1077</t>
         </is>
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>0.4464</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>0.2043</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>0.3232</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>49.93</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>29.47</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>0.1972</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>42.74</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.99</t>
         </is>
       </c>
       <c r="BD71" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3711</t>
         </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="BF71" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="BG71" t="inlineStr">
@@ -20343,12 +20331,12 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ71" t="inlineStr"/>
@@ -22978,34 +22966,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30554,34 +30538,30 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -35763,47 +35743,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>656484</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tristan Gray</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35830,22 +35810,22 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>32.7</v>
+        <v>29.3</v>
       </c>
       <c r="Q127" t="n">
-        <v>43.8</v>
+        <v>34.9</v>
       </c>
       <c r="R127" t="n">
-        <v>68.09999999999999</v>
+        <v>40.2</v>
       </c>
       <c r="S127" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T127" t="n">
         <v>80</v>
       </c>
       <c r="U127" t="n">
-        <v>4.5</v>
+        <v>59.1</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35859,7 +35839,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35897,132 +35877,132 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 6.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>100.6168</t>
+          <t>98.614</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.4224</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1404</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>42.06</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1258</t>
+          <t>0.1703</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>26.81</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH127" t="inlineStr">
@@ -36032,7 +36012,7 @@
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -36043,32 +36023,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>647304</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Josh Naylor</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-11T20:10:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -36078,12 +36058,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -36110,13 +36090,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>29.3</v>
+        <v>24.8</v>
       </c>
       <c r="Q128" t="n">
-        <v>34.9</v>
+        <v>49.5</v>
       </c>
       <c r="R128" t="n">
-        <v>40.2</v>
+        <v>41.1</v>
       </c>
       <c r="S128" t="n">
         <v>86.40000000000001</v>
@@ -36125,7 +36105,7 @@
         <v>80</v>
       </c>
       <c r="U128" t="n">
-        <v>59.1</v>
+        <v>15.3</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -36177,27 +36157,27 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -36207,112 +36187,112 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>38.68</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>98.614</t>
+          <t>99.2618</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.4224</t>
+          <t>0.4073</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.1373</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>70.44</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>23.69</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.1703</t>
+          <t>0.1215</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1807</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH128" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr"/>
@@ -36323,47 +36303,47 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>647304</t>
+          <t>656484</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Josh Naylor</t>
+          <t>Tristan Gray</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-11T20:10:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -36372,7 +36352,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -36390,22 +36370,22 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>24.8</v>
+        <v>32.7</v>
       </c>
       <c r="Q129" t="n">
-        <v>49.5</v>
+        <v>43.8</v>
       </c>
       <c r="R129" t="n">
-        <v>41.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="S129" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T129" t="n">
         <v>80</v>
       </c>
       <c r="U129" t="n">
-        <v>15.3</v>
+        <v>3.4</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -36419,7 +36399,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -36457,12 +36437,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -36472,127 +36452,127 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 6.8 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>40.17</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>99.2618</t>
+          <t>100.6168</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.4073</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1373</t>
+          <t>0.1404</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>70.44</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.06</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>23.69</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1215</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -39766,34 +39746,30 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41166,34 +41142,30 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41730,34 +41702,30 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -44522,34 +44490,30 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB158" t="inlineStr"/>
       <c r="AC158" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -45086,34 +45050,30 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB160" t="inlineStr"/>
       <c r="AC160" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -46490,34 +46450,30 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB165" t="inlineStr"/>
       <c r="AC165" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -50962,34 +50918,30 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -52918,34 +52870,30 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB188" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -54362,7 +54310,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -54372,7 +54320,7 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/14, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
@@ -62392,7 +62340,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -62425,7 +62373,7 @@
         <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>42</v>
+        <v>39.8</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -62482,7 +62430,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -62492,7 +62440,7 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 1 HR</t>
+          <t>Last 7 games: 5/19, 1 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
@@ -64670,34 +64618,30 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X230" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB230" t="inlineStr"/>
       <c r="AC230" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -69339,56 +69283,56 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>645302</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Victor Robles</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2026-07-11T20:10:00Z</t>
+          <t>2026-07-11T18:10:00Z</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L247" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -69402,61 +69346,57 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P247" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="Q247" t="n">
-        <v>49.5</v>
+        <v>31.6</v>
       </c>
       <c r="R247" t="n">
-        <v>41.1</v>
+        <v>40.1</v>
       </c>
       <c r="S247" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T247" t="n">
         <v>50</v>
       </c>
       <c r="U247" t="n">
-        <v>5.7</v>
+        <v>81.7</v>
       </c>
       <c r="V247" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W247" t="inlineStr">
+      <c r="W247" t="inlineStr"/>
+      <c r="X247" t="inlineStr"/>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB247" t="inlineStr"/>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr"/>
@@ -69473,27 +69413,27 @@
       </c>
       <c r="AH247" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL247" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
@@ -69503,112 +69443,112 @@
       </c>
       <c r="AN247" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>33.49</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>87.01</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>94.7182</t>
+          <t>97.9126</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>0.3109</t>
+          <t>0.3243</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>0.0939</t>
+          <t>0.0973</t>
         </is>
       </c>
       <c r="AT247" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.2614</t>
         </is>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>67.98</t>
+          <t>69.28</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>0.0409</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>10.45</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>89.06</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD247" t="inlineStr">
         <is>
-          <t>0.4374</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="BE247" t="inlineStr">
         <is>
-          <t>0.1807</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BF247" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="BG247" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH247" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI247" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ247" t="inlineStr"/>
@@ -69619,22 +69559,22 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>691594</t>
+          <t>645302</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Victor Robles</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -69644,22 +69584,22 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -69668,7 +69608,7 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -69686,22 +69626,22 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>10.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q248" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="R248" t="n">
-        <v>35</v>
+        <v>41.1</v>
       </c>
       <c r="S248" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T248" t="n">
         <v>50</v>
       </c>
       <c r="U248" t="n">
-        <v>10.6</v>
+        <v>5.7</v>
       </c>
       <c r="V248" t="inlineStr">
         <is>
@@ -69715,7 +69655,7 @@
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y248" t="inlineStr">
@@ -69753,12 +69693,12 @@
       </c>
       <c r="AH248" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ248" t="inlineStr">
@@ -69768,12 +69708,12 @@
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL248" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 22.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 10.5 HR allowed</t>
         </is>
       </c>
       <c r="AM248" t="inlineStr">
@@ -69783,87 +69723,87 @@
       </c>
       <c r="AN248" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>32.76</t>
+          <t>20.05</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>97.6261</t>
+          <t>94.7182</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3109</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>0.0739</t>
+          <t>0.0939</t>
         </is>
       </c>
       <c r="AT248" t="inlineStr">
         <is>
-          <t>0.2799</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>69.14</t>
+          <t>67.98</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>29.53</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.0409</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>10.45</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>89.48</t>
+          <t>89.06</t>
         </is>
       </c>
       <c r="BD248" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4374</t>
         </is>
       </c>
       <c r="BE248" t="inlineStr">
@@ -69873,7 +69813,7 @@
       </c>
       <c r="BF248" t="inlineStr">
         <is>
-          <t>27.34</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="BG248" t="inlineStr">
@@ -69888,7 +69828,7 @@
       </c>
       <c r="BI248" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ248" t="inlineStr"/>
@@ -69899,47 +69839,47 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>691594</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T20:10:00Z</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -69948,7 +69888,7 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
@@ -69962,26 +69902,26 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P249" t="n">
-        <v>2.8</v>
+        <v>10.7</v>
       </c>
       <c r="Q249" t="n">
-        <v>35.1</v>
+        <v>50.2</v>
       </c>
       <c r="R249" t="n">
-        <v>41.1</v>
+        <v>35</v>
       </c>
       <c r="S249" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T249" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U249" t="n">
-        <v>38.3</v>
+        <v>10.6</v>
       </c>
       <c r="V249" t="inlineStr">
         <is>
@@ -69995,7 +69935,7 @@
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -70016,7 +69956,7 @@
       <c r="AB249" t="inlineStr"/>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr"/>
@@ -70033,12 +69973,12 @@
       </c>
       <c r="AH249" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ249" t="inlineStr">
@@ -70048,112 +69988,112 @@
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Contact streak: 6/16 over last 7 games</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL249" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 22.1 HR allowed</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN249" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>27.33</t>
+          <t>32.76</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>95.4416</t>
+          <t>97.6261</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>0.2683</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>0.0412</t>
+          <t>0.0739</t>
         </is>
       </c>
       <c r="AT249" t="inlineStr">
         <is>
-          <t>0.2561</t>
+          <t>0.2799</t>
         </is>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>66.86</t>
+          <t>69.14</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>35.41</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>0.0385</t>
+          <t>0.1411</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>40.87</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>89.48</t>
         </is>
       </c>
       <c r="BD249" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="BE249" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1807</t>
         </is>
       </c>
       <c r="BF249" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>27.34</t>
         </is>
       </c>
       <c r="BG249" t="inlineStr">
@@ -70168,7 +70108,7 @@
       </c>
       <c r="BI249" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ249" t="inlineStr"/>
@@ -70179,32 +70119,32 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>682729</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Jonatan Clase</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -70214,12 +70154,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -70242,65 +70182,61 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P250" t="n">
-        <v>7.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q250" t="n">
-        <v>44.5</v>
+        <v>35.1</v>
       </c>
       <c r="R250" t="n">
-        <v>22.6</v>
+        <v>41.1</v>
       </c>
       <c r="S250" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T250" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U250" t="n">
-        <v>41.2</v>
+        <v>38.3</v>
       </c>
       <c r="V250" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr"/>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr"/>
@@ -70312,139 +70248,147 @@
       </c>
       <c r="AG250" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH250" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
         <is>
-          <t>Last 4 games: 3/11, 1 HR</t>
+          <t>Contact streak: 6/16 over last 7 games</t>
         </is>
       </c>
       <c r="AL250" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM250" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN250" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>27.33</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>85.09</t>
+          <t>85.01</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
-          <t>93.3128</t>
+          <t>95.4416</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>0.2528</t>
+          <t>0.2683</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.0412</t>
         </is>
       </c>
       <c r="AT250" t="inlineStr">
         <is>
-          <t>0.1909</t>
+          <t>0.2561</t>
         </is>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>66.86</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>35.41</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.0385</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD250" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE250" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF250" t="inlineStr">
         <is>
-          <t>22.25</t>
-        </is>
-      </c>
-      <c r="BG250" t="inlineStr"/>
-      <c r="BH250" t="inlineStr"/>
+          <t>33.6</t>
+        </is>
+      </c>
+      <c r="BG250" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH250" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI250" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ250" t="inlineStr"/>
@@ -70455,47 +70399,47 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>683083</t>
+          <t>682729</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Nasim Nuñez</t>
+          <t>Jonatan Clase</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-07-11T20:05:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -70504,7 +70448,7 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
@@ -70518,58 +70462,62 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P251" t="n">
-        <v>5</v>
+        <v>7.3</v>
       </c>
       <c r="Q251" t="n">
-        <v>33.9</v>
+        <v>44.5</v>
       </c>
       <c r="R251" t="n">
-        <v>40.2</v>
+        <v>22.6</v>
       </c>
       <c r="S251" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T251" t="n">
         <v>75</v>
       </c>
       <c r="U251" t="n">
-        <v>54.9</v>
+        <v>41.2</v>
       </c>
       <c r="V251" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W251" t="inlineStr">
+      <c r="Z251" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC251" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70584,17 +70532,17 @@
       </c>
       <c r="AG251" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH251" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ251" t="inlineStr">
@@ -70604,127 +70552,119 @@
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 4 games: 3/11, 1 HR</t>
         </is>
       </c>
       <c r="AL251" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN251" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>86.01</t>
+          <t>85.09</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
         <is>
-          <t>96.0075</t>
+          <t>93.3128</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>0.2984</t>
+          <t>0.2528</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="AT251" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.1909</t>
         </is>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>68.77</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD251" t="inlineStr">
         <is>
-          <t>0.3609</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE251" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF251" t="inlineStr">
         <is>
-          <t>26.81</t>
-        </is>
-      </c>
-      <c r="BG251" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH251" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
+          <t>22.25</t>
+        </is>
+      </c>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="inlineStr"/>
       <c r="BI251" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ251" t="inlineStr"/>
@@ -70735,47 +70675,47 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>683083</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Nasim Nuñez</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-07-11T23:15:00Z</t>
+          <t>2026-07-11T20:05:00Z</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -70798,62 +70738,58 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P252" t="n">
-        <v>14.3</v>
+        <v>5</v>
       </c>
       <c r="Q252" t="n">
-        <v>35.4</v>
+        <v>33.9</v>
       </c>
       <c r="R252" t="n">
-        <v>22.1</v>
+        <v>40.2</v>
       </c>
       <c r="S252" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T252" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U252" t="n">
-        <v>10.6</v>
+        <v>54.9</v>
       </c>
       <c r="V252" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr"/>
       <c r="AC252" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -70873,27 +70809,27 @@
       </c>
       <c r="AH252" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL252" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 9.4 HR allowed</t>
         </is>
       </c>
       <c r="AM252" t="inlineStr">
@@ -70903,72 +70839,72 @@
       </c>
       <c r="AN252" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>27.22</t>
         </is>
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>87.95</t>
+          <t>86.01</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
-          <t>98.5487</t>
+          <t>96.0075</t>
         </is>
       </c>
       <c r="AR252" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.2984</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr">
         <is>
+          <t>0.0741</t>
+        </is>
+      </c>
+      <c r="AT252" t="inlineStr">
+        <is>
+          <t>0.2771</t>
+        </is>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>68.77</t>
+        </is>
+      </c>
+      <c r="AV252" t="inlineStr">
+        <is>
+          <t>5.15</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>32.83</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>18.68</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
           <t>0.086</t>
         </is>
       </c>
-      <c r="AT252" t="inlineStr">
-        <is>
-          <t>0.2951</t>
-        </is>
-      </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>70.96</t>
-        </is>
-      </c>
-      <c r="AV252" t="inlineStr">
-        <is>
-          <t>14.5</t>
-        </is>
-      </c>
-      <c r="AW252" t="inlineStr">
-        <is>
-          <t>33.09</t>
-        </is>
-      </c>
-      <c r="AX252" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="AY252" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AZ252" t="inlineStr">
-        <is>
-          <t>0.096</t>
-        </is>
-      </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
@@ -70978,29 +70914,37 @@
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>87.94</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD252" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.3609</t>
         </is>
       </c>
       <c r="BE252" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="BF252" t="inlineStr">
         <is>
-          <t>27.23</t>
-        </is>
-      </c>
-      <c r="BG252" t="inlineStr"/>
-      <c r="BH252" t="inlineStr"/>
+          <t>26.81</t>
+        </is>
+      </c>
+      <c r="BG252" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH252" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
       <c r="BI252" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ252" t="inlineStr"/>
@@ -71011,56 +70955,56 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-07-11T18:10:00Z</t>
+          <t>2026-07-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L253" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
@@ -71074,61 +71018,65 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P253" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="Q253" t="n">
-        <v>31.2</v>
+        <v>35.4</v>
       </c>
       <c r="R253" t="n">
-        <v>40.1</v>
+        <v>22.1</v>
       </c>
       <c r="S253" t="n">
-        <v>44.8</v>
+        <v>71.7</v>
       </c>
       <c r="T253" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U253" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="V253" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W253" t="inlineStr">
+      <c r="Z253" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr"/>
@@ -71145,12 +71093,12 @@
       </c>
       <c r="AH253" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ253" t="inlineStr">
@@ -71160,127 +71108,119 @@
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/18, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL253" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.6% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN253" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.95</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
-          <t>96.0986</t>
+          <t>98.5487</t>
         </is>
       </c>
       <c r="AR253" t="inlineStr">
         <is>
-          <t>0.2114</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>0.0875</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="AT253" t="inlineStr">
         <is>
-          <t>0.1813</t>
+          <t>0.2951</t>
         </is>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>70.96</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>19.99</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD253" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="BE253" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF253" t="inlineStr">
         <is>
-          <t>28.2</t>
-        </is>
-      </c>
-      <c r="BG253" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH253" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+          <t>27.23</t>
+        </is>
+      </c>
+      <c r="BG253" t="inlineStr"/>
+      <c r="BH253" t="inlineStr"/>
       <c r="BI253" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ253" t="inlineStr"/>
@@ -71662,34 +71602,30 @@
       </c>
       <c r="W255" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB255" t="inlineStr"/>
       <c r="AC255" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -71944,28 +71880,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W256" t="inlineStr"/>
-      <c r="X256" t="inlineStr"/>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y256" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB256" t="inlineStr"/>
       <c r="AC256" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -74216,34 +74156,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -75616,34 +75552,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-07-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-11.xlsx
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>65.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>42.9</v>
       </c>
       <c r="R6" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>35.2</v>
       </c>
       <c r="R8" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>42.9</v>
       </c>
       <c r="R12" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>35.2</v>
       </c>
       <c r="R13" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4935,27 +4935,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-11T23:15:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4998,26 +4998,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>61.5</v>
+        <v>53.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="R17" t="n">
-        <v>49.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>87</v>
+        <v>29.2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5069,27 +5069,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5099,112 +5099,112 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>48.01</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>93.63</t>
+          <t>92.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>105.2795</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4736</t>
+          <t>0.4489</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>0.1976</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3452</t>
+          <t>0.3364</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>83.54</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1974</t>
+          <t>0.2073</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.94</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5215,27 +5215,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5245,17 +5245,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>58.1</v>
+        <v>58.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,26 +5278,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>53.7</v>
+        <v>61.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>68.09999999999999</v>
+        <v>49.1</v>
       </c>
       <c r="S18" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>29.2</v>
+        <v>87</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5349,27 +5349,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5379,112 +5379,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>48.01</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.18</t>
+          <t>93.63</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>105.2795</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4489</t>
+          <t>0.4736</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1976</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3364</t>
+          <t>0.3452</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>83.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.2073</t>
+          <t>0.1974</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>56.6</v>
+        <v>56.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>42.9</v>
       </c>
       <c r="R21" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S21" t="n">
         <v>86.40000000000001</v>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8295,27 +8295,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>668939</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-11T22:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8358,26 +8358,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>50.9</v>
+        <v>34.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>36.1</v>
+        <v>41.6</v>
       </c>
       <c r="R29" t="n">
-        <v>44.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T29" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U29" t="n">
-        <v>24.9</v>
+        <v>26.4</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 11.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8459,112 +8459,112 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>11.02</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.2298</t>
+          <t>99.7403</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.5142</t>
+          <t>0.4296</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.2235</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3713</t>
+          <t>0.3418</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>71.91</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.2205</t>
+          <t>0.174</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1319</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>17.67</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8575,47 +8575,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>668939</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T22:10:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8638,26 +8638,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>34.8</v>
+        <v>50.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>41.6</v>
+        <v>36.1</v>
       </c>
       <c r="R30" t="n">
-        <v>68.09999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="S30" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U30" t="n">
-        <v>26.4</v>
+        <v>24.9</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 8/28, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 11.3 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8739,102 +8739,102 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>11.02</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>99.7403</t>
+          <t>101.2298</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4296</t>
+          <t>0.5142</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.2235</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3418</t>
+          <t>0.3713</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>71.91</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>29.76</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>0.2205</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1319</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>17.67</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -8844,7 +8844,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8855,27 +8855,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>621493</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-11T22:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8890,21 +8890,21 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8918,26 +8918,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>54.3</v>
+        <v>32.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>34.5</v>
+        <v>42.9</v>
       </c>
       <c r="R31" t="n">
-        <v>44.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="T31" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/23, 0 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 9.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -9019,112 +9019,112 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>40.25</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>89.54</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>102.1064</t>
+          <t>99.6112</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.5116</t>
+          <t>0.4031</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.2366</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3862</t>
+          <t>0.3428</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>68.59</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.2358</t>
+          <t>0.1413</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3665</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1427</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -9135,32 +9135,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>621493</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T22:10:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9170,21 +9170,21 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9198,26 +9198,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>32.9</v>
+        <v>54.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>42.9</v>
+        <v>34.5</v>
       </c>
       <c r="R32" t="n">
-        <v>68.09999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="S32" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="T32" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9284,12 +9284,12 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 1/23, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9299,102 +9299,102 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>11.81</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>89.54</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.6112</t>
+          <t>102.1064</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.4031</t>
+          <t>0.5116</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.2366</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3428</t>
+          <t>0.3862</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>68.59</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>47.31</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1413</t>
+          <t>0.2358</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3665</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1427</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9975,22 +9975,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>691723</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10005,26 +10005,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10038,26 +10038,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>48.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>35.1</v>
+        <v>42.9</v>
       </c>
       <c r="R35" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S35" t="n">
-        <v>93.2</v>
+        <v>64.3</v>
       </c>
       <c r="T35" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U35" t="n">
-        <v>26.8</v>
+        <v>20.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10092,7 +10092,7 @@
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -10109,12 +10109,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10124,127 +10124,127 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 1 HR</t>
+          <t>Last 7 games: 2/15, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>9.96</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>48.23</t>
+          <t>45.31</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>91.76</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>101.8965</t>
+          <t>102.884</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4322</t>
+          <t>0.3721</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1887</t>
+          <t>0.1663</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3423</t>
+          <t>0.289</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>54.03</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>50.39</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>27.58</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.2037</t>
+          <t>0.185</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10255,22 +10255,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>691723</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10285,26 +10285,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10318,26 +10318,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>43.6</v>
+        <v>48.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>42.9</v>
+        <v>35.1</v>
       </c>
       <c r="R36" t="n">
-        <v>68.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="S36" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T36" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>20.3</v>
+        <v>26.8</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10372,7 +10372,7 @@
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10389,12 +10389,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10404,127 +10404,127 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 1 HR</t>
+          <t>Last 7 games: 3/17, 1 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>9.96</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>45.31</t>
+          <t>48.23</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>91.76</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>102.884</t>
+          <t>101.8965</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.3721</t>
+          <t>0.4322</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1663</t>
+          <t>0.1887</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>0.3423</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>54.03</t>
+          <t>23.47</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>50.39</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>27.58</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.2037</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>35.2</v>
       </c>
       <c r="R43" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S43" t="n">
         <v>86.40000000000001</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
@@ -12491,22 +12491,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -12521,17 +12521,17 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12540,7 +12540,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12554,26 +12554,26 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>41.8</v>
+        <v>44.5</v>
       </c>
       <c r="Q44" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="R44" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S44" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T44" t="n">
         <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>82</v>
+        <v>46.9</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -12608,7 +12608,7 @@
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -12630,137 +12630,137 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>44.04</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.37</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>100.9352</t>
+          <t>100.7366</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.4346</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1939</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3194</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>72.13</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>26.97</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>40.58</t>
+          <t>42.05</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>29.87</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12771,27 +12771,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>682998</t>
+          <t>694671</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12801,17 +12801,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12834,57 +12834,61 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>54.5</v>
+        <v>41.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>27.3</v>
+        <v>35.1</v>
       </c>
       <c r="R45" t="n">
-        <v>38.1</v>
+        <v>41.1</v>
       </c>
       <c r="S45" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T45" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>0.8</v>
+        <v>82</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="Y45" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -12901,142 +12905,142 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>10.15</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>91.54</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>102.4703</t>
+          <t>100.9352</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.4695</t>
+          <t>0.427</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.2138</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3194</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>26.97</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>40.58</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -13047,27 +13051,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>682998</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -13077,17 +13081,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -13096,7 +13100,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -13110,50 +13114,42 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>44.5</v>
+        <v>54.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>35.2</v>
+        <v>27.3</v>
       </c>
       <c r="R46" t="n">
-        <v>68.09999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="S46" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U46" t="n">
-        <v>46.9</v>
+        <v>0.8</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -13161,7 +13157,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13181,27 +13181,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/29, 1 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -13211,112 +13211,112 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>89.37</t>
+          <t>91.54</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>100.7366</t>
+          <t>102.4703</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4346</t>
+          <t>0.4695</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.1939</t>
+          <t>0.2138</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>72.13</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13887,27 +13887,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>683002</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Gunnar Henderson</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -13917,26 +13917,26 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13950,26 +13950,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>45.3</v>
+        <v>37.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>52.5</v>
+        <v>42.9</v>
       </c>
       <c r="R49" t="n">
-        <v>38.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S49" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T49" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
-        <v>54.9</v>
+        <v>0</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14021,27 +14021,27 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
@@ -14051,112 +14051,112 @@
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>46.19</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>101.812</t>
+          <t>101.3682</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.3998</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1774</t>
+          <t>0.1497</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3179</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>74.67</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14167,27 +14167,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>683002</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gunnar Henderson</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14197,26 +14197,26 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -14230,26 +14230,26 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>37.5</v>
+        <v>45.3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42.9</v>
+        <v>52.5</v>
       </c>
       <c r="R50" t="n">
-        <v>68.09999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="S50" t="n">
-        <v>93.2</v>
+        <v>52.4</v>
       </c>
       <c r="T50" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>54.9</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14301,27 +14301,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14331,112 +14331,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>46.19</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>101.3682</t>
+          <t>101.812</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.3998</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1497</t>
+          <t>0.1774</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3179</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>18.03</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -15868,7 +15868,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -17523,27 +17523,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -17558,12 +17558,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17586,17 +17586,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>35.6</v>
+        <v>25.1</v>
       </c>
       <c r="Q62" t="n">
-        <v>52.5</v>
+        <v>35.2</v>
       </c>
       <c r="R62" t="n">
-        <v>38.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S62" t="n">
         <v>94.90000000000001</v>
@@ -17605,7 +17605,7 @@
         <v>50</v>
       </c>
       <c r="U62" t="n">
-        <v>10.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
@@ -17667,132 +17667,132 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>90.29</t>
+          <t>88.64</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>98.6587</t>
+          <t>99.4115</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.4367</t>
+          <t>0.3455</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1208</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3011</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>72.42</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>22.52</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>26.14</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.1746</t>
+          <t>0.1435</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -17803,27 +17803,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -17838,12 +17838,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -17852,7 +17852,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17866,17 +17866,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>25.1</v>
+        <v>35.6</v>
       </c>
       <c r="Q63" t="n">
-        <v>35.2</v>
+        <v>52.5</v>
       </c>
       <c r="R63" t="n">
-        <v>68.09999999999999</v>
+        <v>38.1</v>
       </c>
       <c r="S63" t="n">
         <v>94.90000000000001</v>
@@ -17885,7 +17885,7 @@
         <v>50</v>
       </c>
       <c r="U63" t="n">
-        <v>70.59999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI63" t="inlineStr">
@@ -17947,132 +17947,132 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>88.64</t>
+          <t>90.29</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>99.4115</t>
+          <t>98.6587</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.3455</t>
+          <t>0.4367</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1208</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3011</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>72.42</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1435</t>
+          <t>0.1746</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -19483,22 +19483,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>673962</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -19513,17 +19513,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -19532,7 +19532,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -19546,26 +19546,26 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>34.9</v>
+        <v>31.9</v>
       </c>
       <c r="Q69" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="R69" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S69" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T69" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U69" t="n">
-        <v>52.3</v>
+        <v>24.9</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -19600,7 +19600,7 @@
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr"/>
@@ -19617,142 +19617,142 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>47.96</t>
+          <t>39.16</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>89.67</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>100.5164</t>
+          <t>98.8462</t>
         </is>
       </c>
       <c r="AR69" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>0.3978</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>0.1522</t>
+          <t>0.1542</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr">
         <is>
-          <t>0.3341</t>
+          <t>0.2951</t>
         </is>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>70.51</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>0.1474</t>
+          <t>0.1383</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD69" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ69" t="inlineStr"/>
@@ -19763,22 +19763,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>686681</t>
+          <t>673962</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -19793,17 +19793,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>46.6</v>
+        <v>46.8</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -19826,26 +19826,26 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>31.9</v>
+        <v>34.9</v>
       </c>
       <c r="Q70" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="R70" t="n">
-        <v>68.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="S70" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T70" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U70" t="n">
-        <v>24.9</v>
+        <v>52.3</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -19880,7 +19880,7 @@
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr"/>
@@ -19897,142 +19897,142 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>39.16</t>
+          <t>47.96</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>98.8462</t>
+          <t>100.5164</t>
         </is>
       </c>
       <c r="AR70" t="inlineStr">
         <is>
-          <t>0.3978</t>
+          <t>0.428</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>0.1542</t>
+          <t>0.1522</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr">
         <is>
-          <t>0.2951</t>
+          <t>0.3341</t>
         </is>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>70.51</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
+          <t>21.68</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>0.1474</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>38.2</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>89.1</t>
+        </is>
+      </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="BE70" t="inlineStr">
+        <is>
+          <t>0.148</t>
+        </is>
+      </c>
+      <c r="BF70" t="inlineStr">
+        <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>0.1383</t>
-        </is>
-      </c>
-      <c r="BA70" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="BB70" t="inlineStr">
-        <is>
-          <t>37.08</t>
-        </is>
-      </c>
-      <c r="BC70" t="inlineStr">
-        <is>
-          <t>88.61</t>
-        </is>
-      </c>
-      <c r="BD70" t="inlineStr">
-        <is>
-          <t>0.3627</t>
-        </is>
-      </c>
-      <c r="BE70" t="inlineStr">
-        <is>
-          <t>0.1408</t>
-        </is>
-      </c>
-      <c r="BF70" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr"/>
@@ -20908,7 +20908,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -21723,22 +21723,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -21758,17 +21758,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -21786,26 +21786,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>37.8</v>
+        <v>33.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>46.8</v>
+        <v>42.9</v>
       </c>
       <c r="R77" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S77" t="n">
         <v>52.4</v>
       </c>
       <c r="T77" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U77" t="n">
-        <v>22.8</v>
+        <v>35.6</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21857,27 +21857,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 1 HR</t>
+          <t>Contact streak: 5/14 over last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21887,112 +21887,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>38.35</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>90.02</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>100.6513</t>
+          <t>98.5105</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.3651</t>
+          <t>0.3963</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.1623</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.2878</t>
+          <t>0.3238</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>74.74</t>
+          <t>70.53</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>48.14</t>
+          <t>8.32</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.1458</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22003,27 +22003,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>657757</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -22033,17 +22033,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -22052,7 +22052,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -22070,22 +22070,22 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>37.1</v>
+        <v>37.8</v>
       </c>
       <c r="Q78" t="n">
-        <v>31.7</v>
+        <v>46.8</v>
       </c>
       <c r="R78" t="n">
-        <v>41.6</v>
+        <v>41.1</v>
       </c>
       <c r="S78" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T78" t="n">
         <v>80</v>
       </c>
       <c r="U78" t="n">
-        <v>0.8</v>
+        <v>22.8</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22142,22 +22142,22 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/20, 1 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22167,112 +22167,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>9.55</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.02</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>100.0184</t>
+          <t>100.6513</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.4229</t>
+          <t>0.3651</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1718</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.3337</t>
+          <t>0.2878</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>74.74</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>48.14</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1987</t>
+          <t>0.1458</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.09</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22283,27 +22283,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -22313,26 +22313,26 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22346,26 +22346,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>33.7</v>
+        <v>37.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>42.9</v>
+        <v>31.7</v>
       </c>
       <c r="R79" t="n">
-        <v>68.09999999999999</v>
+        <v>41.6</v>
       </c>
       <c r="S79" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U79" t="n">
-        <v>35.6</v>
+        <v>0.8</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22417,12 +22417,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -22432,12 +22432,12 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Contact streak: 5/14 over last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22447,112 +22447,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>98.5105</t>
+          <t>100.0184</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.3963</t>
+          <t>0.4229</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.1623</t>
+          <t>0.1718</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.3238</t>
+          <t>0.3337</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>70.53</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>8.32</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>40.03</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>22.51</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.1987</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -24239,27 +24239,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>681082</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bryson Stott</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-11T22:10:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -24269,17 +24269,17 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -24288,7 +24288,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -24306,22 +24306,22 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>27.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q86" t="n">
-        <v>34.5</v>
+        <v>34.2</v>
       </c>
       <c r="R86" t="n">
-        <v>44.6</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S86" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T86" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U86" t="n">
-        <v>16.6</v>
+        <v>55.6</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -24373,27 +24373,27 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.5% barrel, 9.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24403,112 +24403,112 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>40.37</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>88.65</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>98.5842</t>
+          <t>100.1703</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.4014</t>
+          <t>0.3471</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1453</t>
+          <t>0.1053</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3192</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>69.82</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>30.97</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>41.38</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>0.1284</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>0.141</t>
-        </is>
-      </c>
-      <c r="BA86" t="inlineStr">
-        <is>
-          <t>7.52</t>
-        </is>
-      </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.3665</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.1427</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -24519,12 +24519,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>687282</t>
+          <t>681082</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Gabriel Rincones Jr.</t>
+          <t>Bryson Stott</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -24544,12 +24544,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -24568,7 +24568,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24586,7 +24586,7 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>34.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q87" t="n">
         <v>34.5</v>
@@ -24595,13 +24595,13 @@
         <v>44.6</v>
       </c>
       <c r="S87" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T87" t="n">
         <v>80</v>
       </c>
       <c r="U87" t="n">
-        <v>34.4</v>
+        <v>16.6</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24636,7 +24636,7 @@
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr"/>
@@ -24653,22 +24653,22 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
@@ -24683,67 +24683,67 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>36.08</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.65</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>101.6285</t>
+          <t>98.5842</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.4014</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1453</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>61.3</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>28.3</t>
+          <t>34.94</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
@@ -24799,47 +24799,47 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>687282</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Gabriel Rincones Jr.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T22:10:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24866,22 +24866,22 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>25.3</v>
+        <v>34.5</v>
       </c>
       <c r="Q88" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="R88" t="n">
-        <v>68.09999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="S88" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T88" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U88" t="n">
-        <v>55.6</v>
+        <v>34.4</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -24916,7 +24916,7 @@
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24933,12 +24933,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -24948,12 +24948,12 @@
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Contact streak: 7/19 over last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.5% barrel, 9.8 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -24963,102 +24963,102 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>40.37</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>100.1703</t>
+          <t>101.6285</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.3471</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1053</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.3192</t>
+          <t>0.217</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>30.97</t>
+          <t>61.3</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>28.3</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1284</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.3665</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1427</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
@@ -25068,7 +25068,7 @@
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -25384,7 +25384,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -25664,7 +25664,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -25944,7 +25944,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -27064,7 +27064,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27904,7 +27904,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28208,7 +28208,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>35.2</v>
       </c>
       <c r="R100" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S100" t="n">
         <v>52.4</v>
@@ -28423,7 +28423,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI100" t="inlineStr">
@@ -28719,22 +28719,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>665750</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Leody Taveras</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -28749,22 +28749,22 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L102" t="n">
@@ -28786,22 +28786,22 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>23.7</v>
+        <v>17.3</v>
       </c>
       <c r="Q102" t="n">
-        <v>35.1</v>
+        <v>41.6</v>
       </c>
       <c r="R102" t="n">
-        <v>41.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S102" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T102" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U102" t="n">
-        <v>30.3</v>
+        <v>18.3</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -28836,7 +28836,7 @@
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr"/>
@@ -28853,12 +28853,12 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -28868,127 +28868,127 @@
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 1 HR</t>
+          <t>Last 7 games: 2/19, 1 HR</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>36.35</t>
+          <t>31.84</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>87.26</t>
+          <t>87.66</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>98.8012</t>
+          <t>98.5524</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.3223</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>0.1295</t>
+          <t>0.1075</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.2975</t>
+          <t>0.2698</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>70.91</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>17.05</t>
+          <t>24.63</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>23.05</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>0.1436</t>
+          <t>0.1123</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.74</t>
         </is>
       </c>
       <c r="BD102" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.4408</t>
         </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1751</t>
         </is>
       </c>
       <c r="BF102" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="BG102" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr"/>
@@ -28999,22 +28999,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>665750</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Leody Taveras</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -29029,26 +29029,26 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -29066,22 +29066,22 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="Q103" t="n">
-        <v>41.6</v>
+        <v>35.1</v>
       </c>
       <c r="R103" t="n">
-        <v>68.09999999999999</v>
+        <v>41.1</v>
       </c>
       <c r="S103" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T103" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U103" t="n">
-        <v>18.3</v>
+        <v>30.3</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -29116,7 +29116,7 @@
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr"/>
@@ -29133,12 +29133,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29148,127 +29148,127 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 1 HR</t>
+          <t>Last 7 games: 3/15, 1 HR</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 12.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>31.84</t>
+          <t>36.35</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>87.66</t>
+          <t>87.26</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>98.5524</t>
+          <t>98.8012</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.3223</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.1075</t>
+          <t>0.1295</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.2698</t>
+          <t>0.2975</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>72.32</t>
+          <t>70.91</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>17.05</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>36.74</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1123</t>
+          <t>0.1436</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>88.74</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.4408</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.1751</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>25.4</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -32376,7 +32376,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -35444,7 +35444,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -36890,7 +36890,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -37170,7 +37170,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>65.59999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>42.9</v>
       </c>
       <c r="R6" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -37689,7 +37689,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -38034,7 +38034,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -38058,7 +38058,7 @@
         <v>35.2</v>
       </c>
       <c r="R8" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -38249,7 +38249,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -39154,7 +39154,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58.8</v>
+        <v>59</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>42.9</v>
       </c>
       <c r="R12" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -39369,7 +39369,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>35.2</v>
       </c>
       <c r="R13" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -39649,7 +39649,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -40505,27 +40505,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-11T23:15:00Z</t>
+          <t>2026-07-11T23:05:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -40535,17 +40535,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Reynaldo López</t>
+          <t>Kyle Bradish</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>625643</t>
+          <t>680694</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -40568,26 +40568,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>61.5</v>
+        <v>53.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="R17" t="n">
-        <v>49.1</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>87</v>
+        <v>29.2</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -40639,27 +40639,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -40669,112 +40669,112 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>48.01</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>93.63</t>
+          <t>92.18</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>105.2795</t>
+          <t>102.93</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4736</t>
+          <t>0.4489</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>0.1976</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3452</t>
+          <t>0.3364</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>74.27</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>83.54</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>39.04</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>29.23</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1974</t>
+          <t>0.2073</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>5.69</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>37.08</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.94</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.3627</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1699</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>27.23</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -40785,27 +40785,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-11T23:05:00Z</t>
+          <t>2026-07-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -40815,17 +40815,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Kyle Bradish</t>
+          <t>Reynaldo López</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>680694</t>
+          <t>625643</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -40834,7 +40834,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>58.1</v>
+        <v>58.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -40848,26 +40848,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>53.7</v>
+        <v>61.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>35.2</v>
+        <v>35.4</v>
       </c>
       <c r="R18" t="n">
-        <v>68.09999999999999</v>
+        <v>49.1</v>
       </c>
       <c r="S18" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>29.2</v>
+        <v>87</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -40919,27 +40919,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 9.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.7% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -40949,112 +40949,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>13.42</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>48.01</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>92.18</t>
+          <t>93.63</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>102.93</t>
+          <t>105.2795</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4489</t>
+          <t>0.4736</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1976</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3364</t>
+          <t>0.3452</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>74.27</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>83.54</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>24.19</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.2073</t>
+          <t>0.1974</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.69</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>37.08</t>
+          <t>39.22</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3627</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1699</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>27.23</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -41674,7 +41674,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>56.6</v>
+        <v>56.8</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -41698,7 +41698,7 @@
         <v>42.9</v>
       </c>
       <c r="R21" t="n">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S21" t="n">
         <v>86.40000000000001</v>
@@ -41889,7 +41889,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-07-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-11.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -21464,7 +21464,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -21744,7 +21744,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -22024,7 +22024,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23144,7 +23144,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -23704,7 +23704,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -24824,7 +24824,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -27616,7 +27616,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28176,7 +28176,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -29288,7 +29288,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -30124,7 +30124,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -30684,7 +30684,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -31290,7 +31290,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -31850,7 +31850,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -32130,7 +32130,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -32410,7 +32410,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -33250,7 +33250,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -33530,7 +33530,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -33810,7 +33810,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -34370,7 +34370,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -34650,7 +34650,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -35210,7 +35210,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -36050,7 +36050,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -36610,7 +36610,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-07-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-07-11.xlsx
@@ -1295,27 +1295,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1358,26 +1358,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47.6</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.5</v>
+        <v>46</v>
       </c>
       <c r="R4" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S4" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>43.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1412,7 +1412,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1459,112 +1459,112 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.8959</t>
+          <t>102.5213</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4943</t>
+          <t>0.451</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2091</t>
+          <t>0.229</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2028</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -1575,27 +1575,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.5</v>
+        <v>56.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,26 +1638,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>58</v>
+        <v>47.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>52.5</v>
       </c>
       <c r="R5" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S5" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>69.09999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1692,7 +1692,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1739,112 +1739,112 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.5213</t>
+          <t>100.8959</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>0.4943</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.2091</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2028</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -2411,27 +2411,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>682998</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2474,54 +2474,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>54.5</v>
+        <v>49.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.3</v>
+        <v>31.7</v>
       </c>
       <c r="R8" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8</v>
+        <v>57.8</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2541,27 +2545,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2571,112 +2575,112 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.54</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.4703</t>
+          <t>101.8062</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4695</t>
+          <t>0.4397</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2138</t>
+          <t>0.1981</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.2102</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -2687,27 +2691,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>682998</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2717,17 +2721,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2736,7 +2740,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2750,58 +2754,54 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.3</v>
+        <v>54.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>31.7</v>
+        <v>27.3</v>
       </c>
       <c r="R9" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S9" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>57.8</v>
+        <v>0.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2851,112 +2851,112 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.8062</t>
+          <t>102.4703</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4397</t>
+          <t>0.4695</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1981</t>
+          <t>0.2138</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2102</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2967,27 +2967,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3030,26 +3030,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>45.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.5</v>
+        <v>31.7</v>
       </c>
       <c r="R10" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S10" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>54.9</v>
+        <v>19.5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3131,112 +3131,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.812</t>
+          <t>100.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.4326</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1774</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3162</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3247,27 +3247,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3277,17 +3277,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3310,26 +3310,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.7</v>
+        <v>52.5</v>
       </c>
       <c r="R11" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>19.5</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3381,27 +3381,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3411,112 +3411,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.25</t>
+          <t>101.812</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4326</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.1774</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3162</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>18.03</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>46</v>
       </c>
       <c r="R13" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -4066,12 +4066,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4087,27 +4087,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>606466</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4136,68 +4136,72 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Strong Barrel, Premium Lineup Spot</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>49.8</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>53.4</v>
-      </c>
       <c r="Q14" t="n">
-        <v>26.1</v>
+        <v>31.7</v>
       </c>
       <c r="R14" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>8.800000000000001</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4217,12 +4221,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4232,127 +4236,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.08</t>
+          <t>92.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>102.9323</t>
+          <t>104.4219</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.5123</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1652</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.26</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>56.56</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>50.17</t>
+          <t>32.56</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.1227</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4363,27 +4367,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>606466</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4398,12 +4402,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4412,7 +4416,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4426,58 +4430,54 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>49.8</v>
+        <v>53.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.7</v>
+        <v>26.1</v>
       </c>
       <c r="R15" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>33.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4497,12 +4497,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4512,127 +4512,127 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.32</t>
+          <t>91.08</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>104.4219</t>
+          <t>102.9323</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.5123</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1652</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>56.56</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>50.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1227</t>
+          <t>0.2172</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>46</v>
       </c>
       <c r="R19" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S19" t="n">
         <v>76.2</v>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>45.4</v>
+        <v>45.8</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>31.7</v>
       </c>
       <c r="R20" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S20" t="n">
         <v>86.40000000000001</v>
@@ -6022,12 +6022,12 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>31.7</v>
       </c>
       <c r="R22" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S22" t="n">
         <v>76.2</v>
@@ -6578,12 +6578,12 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>46</v>
       </c>
       <c r="R23" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -6858,12 +6858,12 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>31.7</v>
       </c>
       <c r="R24" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S24" t="n">
         <v>96.59999999999999</v>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>38.6</v>
+        <v>39</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         <v>31.7</v>
       </c>
       <c r="R27" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S27" t="n">
         <v>64.3</v>
@@ -7974,12 +7974,12 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>38.3</v>
+        <v>38.7</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>46</v>
       </c>
       <c r="R28" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S28" t="n">
         <v>93.2</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>38.1</v>
+        <v>38.5</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8348,7 +8348,7 @@
         <v>46</v>
       </c>
       <c r="R29" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S29" t="n">
         <v>64.3</v>
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -8604,7 +8604,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>37.9</v>
+        <v>38.3</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>31.7</v>
       </c>
       <c r="R30" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S30" t="n">
         <v>52.4</v>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -9111,27 +9111,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>543510</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>James McCann</t>
+          <t>Andrés Giménez</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9174,54 +9174,58 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>29.7</v>
+        <v>7.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>27.3</v>
+        <v>46</v>
       </c>
       <c r="R32" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S32" t="n">
         <v>52.4</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>15.3</v>
+        <v>5.7</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9241,12 +9245,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9256,12 +9260,12 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9271,112 +9275,112 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>100.7366</t>
+          <t>95.9329</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3212</t>
+          <t>0.3295</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1193</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2409</t>
+          <t>0.2786</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>72.47</t>
+          <t>68.39</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>4.79</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>22.53</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0849</t>
+          <t>0.1226</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9387,27 +9391,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>571448</t>
+          <t>682729</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nolan Arenado</t>
+          <t>Jonatan Clase</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9417,17 +9421,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9436,7 +9440,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>34.6</v>
+        <v>34.8</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9450,54 +9454,58 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>18.6</v>
+        <v>7.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>27.3</v>
+        <v>44.5</v>
       </c>
       <c r="R33" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S33" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T33" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U33" t="n">
-        <v>53.3</v>
+        <v>41.2</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9512,147 +9520,147 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 4 games: 3/11, 1 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>85.68</t>
+          <t>85.09</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>97.0227</t>
+          <t>93.3128</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.2528</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1206</t>
+          <t>0.0876</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.2918</t>
+          <t>0.1909</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.35</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>64.83</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>37.35</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1554</t>
+          <t>0.2174</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9663,27 +9671,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>543510</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Andrés Giménez</t>
+          <t>James McCann</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9698,12 +9706,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9712,7 +9720,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9726,58 +9734,54 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>7.2</v>
+        <v>29.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>46</v>
+        <v>27.3</v>
       </c>
       <c r="R34" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S34" t="n">
         <v>52.4</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>5.7</v>
+        <v>15.3</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9797,12 +9801,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9812,12 +9816,12 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Last 7 games: 4/18, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -9827,112 +9831,112 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>6.76</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>95.9329</t>
+          <t>100.7366</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3295</t>
+          <t>0.3212</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.1193</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.2409</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>68.39</t>
+          <t>72.47</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>28.05</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>20.21</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>22.53</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1226</t>
+          <t>0.0849</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9943,27 +9947,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>682729</t>
+          <t>571448</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jonatan Clase</t>
+          <t>Nolan Arenado</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9973,17 +9977,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9992,7 +9996,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10006,58 +10010,54 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>7.3</v>
+        <v>18.6</v>
       </c>
       <c r="Q35" t="n">
-        <v>44.5</v>
+        <v>27.3</v>
       </c>
       <c r="R35" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S35" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T35" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>41.2</v>
+        <v>53.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10072,147 +10072,147 @@
       </c>
       <c r="AG35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 4 games: 3/11, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>85.09</t>
+          <t>85.68</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>93.3128</t>
+          <t>97.0227</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.2528</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.0876</t>
+          <t>0.1206</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.1909</t>
+          <t>0.2918</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>69.35</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>64.83</t>
+          <t>42.94</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>28.14</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.2174</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10548,7 +10548,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>32</v>
+        <v>32.4</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>31.7</v>
       </c>
       <c r="R37" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S37" t="n">
         <v>44.8</v>
@@ -10758,12 +10758,12 @@
       </c>
       <c r="BG37" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
@@ -11665,27 +11665,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>672960</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Kazuma Okamoto</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -11695,17 +11695,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -11728,26 +11728,26 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>47.6</v>
+        <v>58</v>
       </c>
       <c r="Q4" t="n">
-        <v>52.5</v>
+        <v>46</v>
       </c>
       <c r="R4" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S4" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>43.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -11782,7 +11782,7 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -11809,17 +11809,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -11829,112 +11829,112 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>91.4</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.8959</t>
+          <t>102.5213</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4943</t>
+          <t>0.451</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2091</t>
+          <t>0.229</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3745</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>70.32</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>8.89</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2028</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>89.72</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.4262</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>22.25</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -11945,27 +11945,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>672960</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazuma Okamoto</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -11975,17 +11975,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -11994,7 +11994,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>56.5</v>
+        <v>56.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12008,26 +12008,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>58</v>
+        <v>47.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>52.5</v>
       </c>
       <c r="R5" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S5" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>69.09999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -12062,7 +12062,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -12089,17 +12089,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 8/28, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -12109,112 +12109,112 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.4</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.5213</t>
+          <t>100.8959</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>0.4943</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.2091</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.3745</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.32</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>8.89</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>36.54</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2028</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>89.72</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4262</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>22.25</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -12781,27 +12781,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>682998</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Corbin Carroll</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12844,54 +12844,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>54.5</v>
+        <v>49.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.3</v>
+        <v>31.7</v>
       </c>
       <c r="R8" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8</v>
+        <v>57.8</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12911,27 +12915,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -12941,112 +12945,112 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>11.43</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.54</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.4703</t>
+          <t>101.8062</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4695</t>
+          <t>0.4397</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2138</t>
+          <t>0.1981</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3538</t>
+          <t>0.3298</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>55.82</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>21.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>0.2102</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -13057,27 +13061,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>682998</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Corbin Carroll</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13087,17 +13091,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13106,7 +13110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13120,58 +13124,54 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.3</v>
+        <v>54.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>31.7</v>
+        <v>27.3</v>
       </c>
       <c r="R9" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S9" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>57.8</v>
+        <v>0.8</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13191,27 +13191,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -13221,112 +13221,112 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>11.43</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>91.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>101.8062</t>
+          <t>102.4703</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4397</t>
+          <t>0.4695</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1981</t>
+          <t>0.2138</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3538</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>55.82</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>46.18</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2102</t>
+          <t>0.247</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -13337,27 +13337,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>687221</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dalton Rushing</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -13367,17 +13367,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13386,7 +13386,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13400,26 +13400,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>45.3</v>
+        <v>43.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>52.5</v>
+        <v>31.7</v>
       </c>
       <c r="R10" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S10" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>54.9</v>
+        <v>19.5</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -13471,27 +13471,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -13501,112 +13501,112 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>12.46</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>44.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.812</t>
+          <t>100.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4147</t>
+          <t>0.4326</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1774</t>
+          <t>0.1864</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.3162</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>18.03</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>27.89</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1935</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>89.82</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.4457</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>21.24</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -13617,27 +13617,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>687221</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Dalton Rushing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -13647,17 +13647,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -13666,7 +13666,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13680,26 +13680,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.3</v>
+        <v>45.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.7</v>
+        <v>52.5</v>
       </c>
       <c r="R11" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>19.5</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -13751,27 +13751,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.8% barrel, 13.4 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -13781,112 +13781,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>12.46</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.09</t>
+          <t>44.46</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.25</t>
+          <t>101.812</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4326</t>
+          <t>0.4147</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1864</t>
+          <t>0.1774</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3162</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>72.61</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>18.03</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.89</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1935</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>41.46</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>89.82</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.4457</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>21.24</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -13946,7 +13946,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>46</v>
       </c>
       <c r="R12" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S12" t="n">
         <v>96.59999999999999</v>
@@ -14156,12 +14156,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -14226,7 +14226,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>46</v>
       </c>
       <c r="R13" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S13" t="n">
         <v>94.90000000000001</v>
@@ -14436,12 +14436,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -14457,27 +14457,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>606466</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ketel Marte</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-12T01:10:00Z</t>
+          <t>2026-07-12T00:40:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14492,12 +14492,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14506,68 +14506,72 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Strong Barrel, Premium Lineup Spot</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>49.8</v>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>53.4</v>
-      </c>
       <c r="Q14" t="n">
-        <v>26.1</v>
+        <v>31.7</v>
       </c>
       <c r="R14" t="n">
-        <v>38.1</v>
+        <v>44.1</v>
       </c>
       <c r="S14" t="n">
         <v>93.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>8.800000000000001</v>
+        <v>33.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14587,12 +14591,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -14602,127 +14606,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>11.75</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>52.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>91.08</t>
+          <t>92.32</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>102.9323</t>
+          <t>104.4219</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.5123</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2189</t>
+          <t>0.1652</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.26</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>56.56</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>50.17</t>
+          <t>32.56</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>21.03</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2172</t>
+          <t>0.1227</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>43.44</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>90.22</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.45</t>
+          <t>25.39</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14733,27 +14737,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>606466</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Ketel Marte</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-12T00:40:00Z</t>
+          <t>2026-07-12T01:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -14768,12 +14772,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14782,7 +14786,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14796,58 +14800,54 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>49.8</v>
+        <v>53.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>31.7</v>
+        <v>26.1</v>
       </c>
       <c r="R15" t="n">
-        <v>41.6</v>
+        <v>38.1</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>33.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14867,12 +14867,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -14882,127 +14882,127 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 4.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 11.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>11.75</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>52.64</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.32</t>
+          <t>91.08</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>104.4219</t>
+          <t>102.9323</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.5123</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1652</t>
+          <t>0.2189</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>75.26</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>56.56</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>50.17</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>27.36</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1227</t>
+          <t>0.2172</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>90.22</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>22.45</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -15902,7 +15902,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46</v>
       </c>
       <c r="R19" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S19" t="n">
         <v>76.2</v>
@@ -16112,12 +16112,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -16182,7 +16182,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>45.4</v>
+        <v>45.8</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>31.7</v>
       </c>
       <c r="R20" t="n">
-        <v>41.6</v>
+        <v>44.1</v>
       </c>
       <c r="S20" t="n">
         <v>86.40000000000001</v>
@@ -16392,12 +16392,12 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
